--- a/MECÂNICAS/PAUTA M/JHONSON/Campanha Johnson - Merchandising - FY26.xlsx
+++ b/MECÂNICAS/PAUTA M/JHONSON/Campanha Johnson - Merchandising - FY26.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\victor.n\PROJETO\MECÂNICAS\PAUTA M\JHONSON\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="B:\Nicolas\Acompanhamentos\JOHNSON\2025.26\Q4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ED06D41-0C13-4CCE-8C20-714AA8276FA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB6E494B-C73A-4E85-9337-F68841F065B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{FB3810CD-89DA-4B85-A0EE-CE6518C3D397}"/>
   </bookViews>
@@ -1546,9 +1546,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>503062</xdr:colOff>
+      <xdr:colOff>509412</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>107203</xdr:rowOff>
+      <xdr:rowOff>100853</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1612,8 +1612,8 @@
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>951915</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>180976</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1701,7 +1701,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>904876</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>68457</xdr:rowOff>
+      <xdr:rowOff>62107</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2124,7 +2124,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B37:E45"/>
+  <dimension ref="B37:E44"/>
   <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="0.54296875" customWidth="1"/>
@@ -2136,7 +2136,7 @@
     <col min="13" max="13" width="9.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="37" spans="2:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="C37" s="1" t="s">
         <v>0</v>
       </c>
@@ -2147,7 +2147,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="2:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2162,7 +2162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="2:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B39" s="2" t="s">
         <v>4</v>
       </c>
@@ -2177,7 +2177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="2:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B40" s="2" t="s">
         <v>5</v>
       </c>
@@ -2192,7 +2192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="2:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B41" s="2" t="s">
         <v>6</v>
       </c>
@@ -2205,7 +2205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="2:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B42" s="5" t="s">
         <v>7</v>
       </c>
@@ -2220,7 +2220,7 @@
         <v>0.15833333333333333</v>
       </c>
     </row>
-    <row r="43" spans="2:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B43" s="2" t="s">
         <v>8</v>
       </c>
@@ -2235,7 +2235,7 @@
         <v>0.15833333333333333</v>
       </c>
     </row>
-    <row r="44" spans="2:5" ht="15" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="2:5" ht="15" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B44" s="6" t="s">
         <v>9</v>
       </c>
@@ -2252,11 +2252,10 @@
         <v>0.15833333333333333</v>
       </c>
     </row>
-    <row r="45" spans="2:5" collapsed="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
-  <pageSetup paperSize="9" scale="72" orientation="portrait" horizontalDpi="4294967293" verticalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="69" orientation="portrait" horizontalDpi="4294967293" verticalDpi="300" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>

--- a/MECÂNICAS/PAUTA M/JHONSON/Campanha Johnson - Merchandising - FY26.xlsx
+++ b/MECÂNICAS/PAUTA M/JHONSON/Campanha Johnson - Merchandising - FY26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="B:\Nicolas\Acompanhamentos\JOHNSON\2025.26\Q4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB6E494B-C73A-4E85-9337-F68841F065B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95367251-2E3A-4BCF-BE55-02F7A90445B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{FB3810CD-89DA-4B85-A0EE-CE6518C3D397}"/>
   </bookViews>
